--- a/Formulas & Functions/Text-Functions/8_Text_Functions_solution.xlsx
+++ b/Formulas & Functions/Text-Functions/8_Text_Functions_solution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\my-excel-journey\Formulas &amp; Functions\Text-Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09011C3E-8007-4F15-8A15-00D49D2E3088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64E4B8C-EA91-45B7-9E4D-C4D40D9BD494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1792,12 +1792,12 @@
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="1"/>
     <col min="2" max="2" width="14.26171875" customWidth="1"/>
-    <col min="3" max="3" width="27.26171875" customWidth="1"/>
-    <col min="4" max="4" width="17.578125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.26171875" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="3" max="3" width="27.26171875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="17.578125" style="9" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="26.26171875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="22" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="40" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="8.83984375" customWidth="1"/>
     <col min="10" max="10" width="34.734375" customWidth="1"/>
     <col min="11" max="11" width="8.83984375" customWidth="1"/>
@@ -1885,6 +1885,13 @@
         <f>_xlfn.TEXTJOIN(" ",TRUE,F2,G2)</f>
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" ref="L2:M2">_xlfn.TEXTSPLIT(B2," ")</f>
+        <v>Pam</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Beesly</v>
+      </c>
       <c r="Q2">
         <f>FIND(",", G2)+LEN(", ")</f>
         <v>11</v>
@@ -1927,6 +1934,13 @@
         <f t="shared" ref="J3:J21" si="0">_xlfn.TEXTJOIN(" ",TRUE,F3,G3)</f>
         <v>203 Birch St Chicago, IL, 60601</v>
       </c>
+      <c r="L3" t="str" cm="1">
+        <f t="array" ref="L3:M3">_xlfn.TEXTSPLIT(B3," ")</f>
+        <v>Michael</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Scott</v>
+      </c>
       <c r="Q3">
         <f t="shared" ref="Q3:Q21" si="1">FIND(",", G3)+LEN(", ")</f>
         <v>10</v>
@@ -1969,6 +1983,13 @@
         <f t="shared" si="0"/>
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
+      <c r="L4" t="str" cm="1">
+        <f t="array" ref="L4:M4">_xlfn.TEXTSPLIT(B4," ")</f>
+        <v>Kevin</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Malone</v>
+      </c>
       <c r="Q4">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2011,6 +2032,13 @@
         <f t="shared" si="0"/>
         <v>457 Oak St San Jose, CA, 95101</v>
       </c>
+      <c r="L5" t="str" cm="1">
+        <f t="array" ref="L5:M5">_xlfn.TEXTSPLIT(B5," ")</f>
+        <v>Pam</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Beesly</v>
+      </c>
       <c r="Q5">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -2053,6 +2081,13 @@
         <f t="shared" si="0"/>
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
+      <c r="L6" t="str" cm="1">
+        <f t="array" ref="L6:M6">_xlfn.TEXTSPLIT(B6," ")</f>
+        <v>Jim</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Halpert</v>
+      </c>
       <c r="Q6">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2095,6 +2130,13 @@
         <f t="shared" si="0"/>
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
+      <c r="L7" t="str" cm="1">
+        <f t="array" ref="L7:M7">_xlfn.TEXTSPLIT(B7," ")</f>
+        <v>Ryan</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Howard</v>
+      </c>
       <c r="Q7">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2137,6 +2179,13 @@
         <f t="shared" si="0"/>
         <v>790 Pine St Chicago, IL, 60601</v>
       </c>
+      <c r="L8" t="str" cm="1">
+        <f t="array" ref="L8:M8">_xlfn.TEXTSPLIT(B8," ")</f>
+        <v>Kevin</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Malone</v>
+      </c>
       <c r="Q8">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2179,6 +2228,13 @@
         <f t="shared" si="0"/>
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
+      <c r="L9" t="str" cm="1">
+        <f t="array" ref="L9:M9">_xlfn.TEXTSPLIT(B9," ")</f>
+        <v>Ryan</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Howard</v>
+      </c>
       <c r="Q9">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2221,6 +2277,13 @@
         <f t="shared" si="0"/>
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
+      <c r="L10" t="str" cm="1">
+        <f t="array" ref="L10:M10">_xlfn.TEXTSPLIT(B10," ")</f>
+        <v>Stanley</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Hudson</v>
+      </c>
       <c r="Q10">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2263,6 +2326,13 @@
         <f t="shared" si="0"/>
         <v>123 Elm St Los Angeles, CA, 90001</v>
       </c>
+      <c r="L11" t="str" cm="1">
+        <f t="array" ref="L11:M11">_xlfn.TEXTSPLIT(B11," ")</f>
+        <v>Angela</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Martin</v>
+      </c>
       <c r="Q11">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -2305,6 +2375,13 @@
         <f t="shared" si="0"/>
         <v>123 Elm St San Diego, CA, 92101</v>
       </c>
+      <c r="L12" t="str" cm="1">
+        <f t="array" ref="L12:M12">_xlfn.TEXTSPLIT(B12," ")</f>
+        <v>Dwight</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Schrute</v>
+      </c>
       <c r="Q12">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -2347,6 +2424,13 @@
         <f t="shared" si="0"/>
         <v>202 Birch St Chicago, IL, 60601</v>
       </c>
+      <c r="L13" t="str" cm="1">
+        <f t="array" ref="L13:M13">_xlfn.TEXTSPLIT(B13," ")</f>
+        <v>Oscar</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Martinez</v>
+      </c>
       <c r="Q13">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2389,6 +2473,13 @@
         <f t="shared" si="0"/>
         <v>204 Birch St Philadelphia, PA, 19101</v>
       </c>
+      <c r="L14" t="str" cm="1">
+        <f t="array" ref="L14:M14">_xlfn.TEXTSPLIT(B14," ")</f>
+        <v>Ryan</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Howard</v>
+      </c>
       <c r="Q14">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2431,6 +2522,13 @@
         <f t="shared" si="0"/>
         <v>123 Elm St Chicago, IL, 60601</v>
       </c>
+      <c r="L15" t="str" cm="1">
+        <f t="array" ref="L15:M15">_xlfn.TEXTSPLIT(B15," ")</f>
+        <v>Phyllis</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Vance</v>
+      </c>
       <c r="Q15">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2473,6 +2571,13 @@
         <f>_xlfn.TEXTJOIN(" ",TRUE,F16,G16)</f>
         <v>456 Oak St Chicago, IL, 60601</v>
       </c>
+      <c r="L16" t="str" cm="1">
+        <f t="array" ref="L16:M16">_xlfn.TEXTSPLIT(B16," ")</f>
+        <v>Meredith</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Palmer</v>
+      </c>
       <c r="Q16">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2515,6 +2620,13 @@
         <f t="shared" si="0"/>
         <v>203 Birch St Chicago, IL, 60602</v>
       </c>
+      <c r="L17" t="str" cm="1">
+        <f t="array" ref="L17:M17">_xlfn.TEXTSPLIT(B17," ")</f>
+        <v>Michael</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Scott</v>
+      </c>
       <c r="Q17">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -2557,6 +2669,13 @@
         <f t="shared" si="0"/>
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
+      <c r="L18" t="str" cm="1">
+        <f t="array" ref="L18:M18">_xlfn.TEXTSPLIT(B18," ")</f>
+        <v>Jim</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Halpert</v>
+      </c>
       <c r="Q18">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2599,6 +2718,13 @@
         <f t="shared" si="0"/>
         <v>456 Oak St New York, NY, 10001</v>
       </c>
+      <c r="L19" t="str" cm="1">
+        <f t="array" ref="L19:M19">_xlfn.TEXTSPLIT(B19," ")</f>
+        <v>Kelly</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Kapoor</v>
+      </c>
       <c r="Q19">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -2641,6 +2767,13 @@
         <f t="shared" si="0"/>
         <v>459 Oak St Philadelphia, PA, 19101</v>
       </c>
+      <c r="L20" t="str" cm="1">
+        <f t="array" ref="L20:M20">_xlfn.TEXTSPLIT(B20," ")</f>
+        <v>Jim</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Halpert</v>
+      </c>
       <c r="Q20">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2682,6 +2815,13 @@
       <c r="J21" t="str">
         <f t="shared" si="0"/>
         <v>459 Oak St New York, NY, 10001</v>
+      </c>
+      <c r="L21" t="str" cm="1">
+        <f t="array" ref="L21:M21">_xlfn.TEXTSPLIT(B21," ")</f>
+        <v>Jim</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Halpert</v>
       </c>
       <c r="Q21">
         <f t="shared" si="1"/>

--- a/Formulas & Functions/Text-Functions/8_Text_Functions_solution.xlsx
+++ b/Formulas & Functions/Text-Functions/8_Text_Functions_solution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\my-excel-journey\Formulas &amp; Functions\Text-Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64E4B8C-EA91-45B7-9E4D-C4D40D9BD494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97C0276-0EA2-4A65-BA13-4776253ECCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1892,6 +1892,10 @@
       <c r="M2" t="str">
         <v>Beesly</v>
       </c>
+      <c r="O2" t="str">
+        <f>RIGHT(A2,7)</f>
+        <v>0123548</v>
+      </c>
       <c r="Q2">
         <f>FIND(",", G2)+LEN(", ")</f>
         <v>11</v>
@@ -1941,16 +1945,20 @@
       <c r="M3" t="str">
         <v>Scott</v>
       </c>
+      <c r="O3" t="str">
+        <f t="shared" ref="O3:O21" si="1">RIGHT(A3,7)</f>
+        <v>0123549</v>
+      </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q21" si="1">FIND(",", G3)+LEN(", ")</f>
+        <f t="shared" ref="Q3:Q21" si="2">FIND(",", G3)+LEN(", ")</f>
         <v>10</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R21" si="2">FIND(",",G3,Q3)</f>
+        <f t="shared" ref="R3:R21" si="3">FIND(",",G3,Q3)</f>
         <v>12</v>
       </c>
       <c r="S3" t="str">
-        <f t="shared" ref="S3:S21" si="3">MID(G3,Q3,R3-Q3)</f>
+        <f t="shared" ref="S3:S21" si="4">MID(G3,Q3,R3-Q3)</f>
         <v>IL</v>
       </c>
     </row>
@@ -1990,16 +1998,20 @@
       <c r="M4" t="str">
         <v>Malone</v>
       </c>
+      <c r="O4" t="str">
+        <f t="shared" si="1"/>
+        <v>0123550</v>
+      </c>
       <c r="Q4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
     </row>
@@ -2039,16 +2051,20 @@
       <c r="M5" t="str">
         <v>Beesly</v>
       </c>
+      <c r="O5" t="str">
+        <f t="shared" si="1"/>
+        <v>0123551</v>
+      </c>
       <c r="Q5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="R5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CA</v>
       </c>
     </row>
@@ -2088,16 +2104,20 @@
       <c r="M6" t="str">
         <v>Halpert</v>
       </c>
+      <c r="O6" t="str">
+        <f t="shared" si="1"/>
+        <v>0123552</v>
+      </c>
       <c r="Q6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S6" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
     </row>
@@ -2137,16 +2157,20 @@
       <c r="M7" t="str">
         <v>Howard</v>
       </c>
+      <c r="O7" t="str">
+        <f t="shared" si="1"/>
+        <v>0123553</v>
+      </c>
       <c r="Q7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
     </row>
@@ -2186,16 +2210,20 @@
       <c r="M8" t="str">
         <v>Malone</v>
       </c>
+      <c r="O8" t="str">
+        <f t="shared" si="1"/>
+        <v>0123554</v>
+      </c>
       <c r="Q8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S8" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
     </row>
@@ -2235,16 +2263,20 @@
       <c r="M9" t="str">
         <v>Howard</v>
       </c>
+      <c r="O9" t="str">
+        <f t="shared" si="1"/>
+        <v>0123555</v>
+      </c>
       <c r="Q9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S9" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
     </row>
@@ -2284,16 +2316,20 @@
       <c r="M10" t="str">
         <v>Hudson</v>
       </c>
+      <c r="O10" t="str">
+        <f t="shared" si="1"/>
+        <v>0123556</v>
+      </c>
       <c r="Q10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
     </row>
@@ -2333,16 +2369,20 @@
       <c r="M11" t="str">
         <v>Martin</v>
       </c>
+      <c r="O11" t="str">
+        <f t="shared" si="1"/>
+        <v>0123557</v>
+      </c>
       <c r="Q11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="R11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="S11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CA</v>
       </c>
     </row>
@@ -2382,16 +2422,20 @@
       <c r="M12" t="str">
         <v>Schrute</v>
       </c>
+      <c r="O12" t="str">
+        <f t="shared" si="1"/>
+        <v>0123558</v>
+      </c>
       <c r="Q12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="R12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="S12" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>CA</v>
       </c>
     </row>
@@ -2431,16 +2475,20 @@
       <c r="M13" t="str">
         <v>Martinez</v>
       </c>
+      <c r="O13" t="str">
+        <f t="shared" si="1"/>
+        <v>0123559</v>
+      </c>
       <c r="Q13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
     </row>
@@ -2480,16 +2528,20 @@
       <c r="M14" t="str">
         <v>Howard</v>
       </c>
+      <c r="O14" t="str">
+        <f t="shared" si="1"/>
+        <v>0123560</v>
+      </c>
       <c r="Q14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
     </row>
@@ -2529,16 +2581,20 @@
       <c r="M15" t="str">
         <v>Vance</v>
       </c>
+      <c r="O15" t="str">
+        <f t="shared" si="1"/>
+        <v>0123561</v>
+      </c>
       <c r="Q15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
     </row>
@@ -2578,16 +2634,20 @@
       <c r="M16" t="str">
         <v>Palmer</v>
       </c>
+      <c r="O16" t="str">
+        <f t="shared" si="1"/>
+        <v>0123562</v>
+      </c>
       <c r="Q16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
     </row>
@@ -2627,16 +2687,20 @@
       <c r="M17" t="str">
         <v>Scott</v>
       </c>
+      <c r="O17" t="str">
+        <f t="shared" si="1"/>
+        <v>0123563</v>
+      </c>
       <c r="Q17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="R17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>IL</v>
       </c>
     </row>
@@ -2676,16 +2740,20 @@
       <c r="M18" t="str">
         <v>Halpert</v>
       </c>
+      <c r="O18" t="str">
+        <f t="shared" si="1"/>
+        <v>0123564</v>
+      </c>
       <c r="Q18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
     </row>
@@ -2725,16 +2793,20 @@
       <c r="M19" t="str">
         <v>Kapoor</v>
       </c>
+      <c r="O19" t="str">
+        <f t="shared" si="1"/>
+        <v>0123565</v>
+      </c>
       <c r="Q19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="R19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S19" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>NY</v>
       </c>
     </row>
@@ -2774,16 +2846,20 @@
       <c r="M20" t="str">
         <v>Halpert</v>
       </c>
+      <c r="O20" t="str">
+        <f t="shared" si="1"/>
+        <v>0123566</v>
+      </c>
       <c r="Q20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="S20" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>PA</v>
       </c>
     </row>
@@ -2823,16 +2899,20 @@
       <c r="M21" t="str">
         <v>Halpert</v>
       </c>
+      <c r="O21" t="str">
+        <f t="shared" si="1"/>
+        <v>0123567</v>
+      </c>
       <c r="Q21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="R21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="S21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>NY</v>
       </c>
     </row>

--- a/Formulas & Functions/Text-Functions/8_Text_Functions_solution.xlsx
+++ b/Formulas & Functions/Text-Functions/8_Text_Functions_solution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\my-excel-journey\Formulas &amp; Functions\Text-Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97C0276-0EA2-4A65-BA13-4776253ECCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF957B5-E06B-4326-9C52-21A3EF083CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1791,20 +1791,20 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="1"/>
-    <col min="2" max="2" width="14.26171875" customWidth="1"/>
+    <col min="2" max="2" width="14.1015625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="27.26171875" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="17.578125" style="9" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="26.26171875" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="11" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="22" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="40" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="34.68359375" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="8.83984375" customWidth="1"/>
-    <col min="10" max="10" width="34.734375" customWidth="1"/>
-    <col min="11" max="11" width="8.83984375" customWidth="1"/>
-    <col min="12" max="12" width="13.3125" customWidth="1"/>
-    <col min="13" max="13" width="15.47265625" customWidth="1"/>
-    <col min="14" max="14" width="8.83984375" customWidth="1"/>
-    <col min="15" max="15" width="16.41796875" customWidth="1"/>
+    <col min="10" max="10" width="34.734375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="8.83984375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13.3125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="15.47265625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="8.83984375" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="16.41796875" hidden="1" customWidth="1"/>
     <col min="17" max="19" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1908,6 +1908,18 @@
         <f>MID(G2,Q2,R2-Q2)</f>
         <v>CA</v>
       </c>
+      <c r="T2">
+        <f>FIND(",",G2)+2</f>
+        <v>11</v>
+      </c>
+      <c r="U2">
+        <f>FIND(",",G2,T2)</f>
+        <v>13</v>
+      </c>
+      <c r="V2" t="str">
+        <f>MID(G2,T2,U2-T2)</f>
+        <v>CA</v>
+      </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
@@ -1961,6 +1973,18 @@
         <f t="shared" ref="S3:S21" si="4">MID(G3,Q3,R3-Q3)</f>
         <v>IL</v>
       </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T21" si="5">FIND(",",G3)+2</f>
+        <v>10</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U21" si="6">FIND(",",G3,T3)</f>
+        <v>12</v>
+      </c>
+      <c r="V3" t="str">
+        <f t="shared" ref="V3:V21" si="7">MID(G3,T3,U3-T3)</f>
+        <v>IL</v>
+      </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
@@ -2014,6 +2038,18 @@
         <f t="shared" si="4"/>
         <v>IL</v>
       </c>
+      <c r="T4">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V4" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
@@ -2067,6 +2103,18 @@
         <f t="shared" si="4"/>
         <v>CA</v>
       </c>
+      <c r="T5">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="V5" t="str">
+        <f t="shared" si="7"/>
+        <v>CA</v>
+      </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
@@ -2120,6 +2168,18 @@
         <f t="shared" si="4"/>
         <v>PA</v>
       </c>
+      <c r="T6">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V6" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
@@ -2173,6 +2233,18 @@
         <f t="shared" si="4"/>
         <v>PA</v>
       </c>
+      <c r="T7">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V7" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
@@ -2226,6 +2298,18 @@
         <f t="shared" si="4"/>
         <v>IL</v>
       </c>
+      <c r="T8">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V8" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
@@ -2279,6 +2363,18 @@
         <f t="shared" si="4"/>
         <v>PA</v>
       </c>
+      <c r="T9">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V9" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
@@ -2332,6 +2428,18 @@
         <f t="shared" si="4"/>
         <v>IL</v>
       </c>
+      <c r="T10">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V10" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
@@ -2385,6 +2493,18 @@
         <f t="shared" si="4"/>
         <v>CA</v>
       </c>
+      <c r="T11">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="V11" t="str">
+        <f t="shared" si="7"/>
+        <v>CA</v>
+      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
@@ -2438,6 +2558,18 @@
         <f t="shared" si="4"/>
         <v>CA</v>
       </c>
+      <c r="T12">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="V12" t="str">
+        <f t="shared" si="7"/>
+        <v>CA</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
@@ -2491,6 +2623,18 @@
         <f t="shared" si="4"/>
         <v>IL</v>
       </c>
+      <c r="T13">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V13" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
@@ -2544,6 +2688,18 @@
         <f t="shared" si="4"/>
         <v>PA</v>
       </c>
+      <c r="T14">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V14" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
@@ -2597,6 +2753,18 @@
         <f t="shared" si="4"/>
         <v>IL</v>
       </c>
+      <c r="T15">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V15" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
@@ -2650,8 +2818,20 @@
         <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="T16">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V16" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -2703,8 +2883,20 @@
         <f t="shared" si="4"/>
         <v>IL</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="T17">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="V17" t="str">
+        <f t="shared" si="7"/>
+        <v>IL</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5" t="s">
         <v>87</v>
       </c>
@@ -2756,8 +2948,20 @@
         <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="T18">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V18" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5" t="s">
         <v>88</v>
       </c>
@@ -2809,8 +3013,20 @@
         <f t="shared" si="4"/>
         <v>NY</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="T19">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="V19" t="str">
+        <f t="shared" si="7"/>
+        <v>NY</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5" t="s">
         <v>89</v>
       </c>
@@ -2862,8 +3078,20 @@
         <f t="shared" si="4"/>
         <v>PA</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="T20">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="V20" t="str">
+        <f t="shared" si="7"/>
+        <v>PA</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
@@ -2913,6 +3141,18 @@
       </c>
       <c r="S21" t="str">
         <f t="shared" si="4"/>
+        <v>NY</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="V21" t="str">
+        <f t="shared" si="7"/>
         <v>NY</v>
       </c>
     </row>

--- a/Formulas & Functions/Text-Functions/8_Text_Functions_solution.xlsx
+++ b/Formulas & Functions/Text-Functions/8_Text_Functions_solution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\my-excel-journey\Formulas &amp; Functions\Text-Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF957B5-E06B-4326-9C52-21A3EF083CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD2C621-E24F-4300-92F0-77DE5A429D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -396,7 +396,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -524,11 +524,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -549,6 +560,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,31 +593,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Skill Count of Applicants</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -770,7 +757,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F30C-45CA-B8A0-F5AF8B1DA29B}"/>
+              <c16:uniqueId val="{00000000-D91C-4CBD-80E3-F9529184CAB7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -783,11 +770,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="1389519888"/>
-        <c:axId val="1389514128"/>
+        <c:axId val="1705220015"/>
+        <c:axId val="1705215695"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1389519888"/>
+        <c:axId val="1705220015"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -830,7 +817,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1389514128"/>
+        <c:crossAx val="1705215695"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -838,7 +825,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1389514128"/>
+        <c:axId val="1705215695"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -889,7 +876,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1389519888"/>
+        <c:crossAx val="1705220015"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1487,23 +1474,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>588963</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>7938</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>4763</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>30163</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>117475</xdr:rowOff>
+      <xdr:colOff>90488</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8C6A45A-EB32-62D3-58CF-3F02DAF72B23}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{191575EF-754C-671D-CFDA-700E461C15B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1797,7 +1784,7 @@
     <col min="5" max="5" width="26.26171875" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="11" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="34.68359375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="34.68359375" customWidth="1"/>
     <col min="9" max="9" width="8.83984375" customWidth="1"/>
     <col min="10" max="10" width="34.734375" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="8.83984375" hidden="1" customWidth="1"/>
@@ -5544,6 +5531,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="24.41796875" customWidth="1"/>
+    <col min="2" max="2" width="17.47265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:75" x14ac:dyDescent="0.55000000000000004">
@@ -5554,7 +5542,7 @@
     </row>
     <row r="3" spans="1:75" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="str">
-        <f>_xlfn.TEXTJOIN(", ",TRUE,Data!H2:H21)</f>
+        <f>_xlfn.TEXTJOIN(", ",TRUE,Data!$H$2:$H$21)</f>
         <v>Kafka, DataBricks, Spark, Python, GCP, Power BI, GCP, Airflow, Hadoop, R, Azure, Java, SQL, DataBricks, Kafka, DataBricks, Spark, Python, GCP, DataBricks, Hadoop, Java, Snowflake, Airflow, DataBricks, Azure, Java, SQL, DataBricks, Snowflake, Airflow, DataBricks, Scala, Azure, R, Kafka, Snowflake, Excel, Scala, Excel, Power BI, R, Scala, R, Hadoop, Power BI, SQL, Snowflake, Airflow, DataBricks, Java, Scala, R, DataBricks, Azure, Scala, Power BI, GCP, Airflow, Hadoop, R, DataBricks, Hadoop, Java, Snowflake, Power BI, Tableau, Airflow, SQL, DataBricks, Hadoop, Java, DataBricks, Hadoop, Java</v>
       </c>
     </row>
@@ -5819,7 +5807,7 @@
         <v>DataBricks</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" ref="B10:B25" si="0">COUNTIF($6:$6,A10)</f>
+        <f t="shared" ref="B10:B24" si="0">COUNTIF($6:$6,A10)</f>
         <v>12</v>
       </c>
     </row>
@@ -5950,12 +5938,12 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>0</v>
       </c>
-      <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="B25" s="18">
+        <f>SUM(B9:B24)</f>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
